--- a/src/test/resources/ImportTemplate/Checksum - Flat File-SQL.xlsx
+++ b/src/test/resources/ImportTemplate/Checksum - Flat File-SQL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1CCC9A-60B1-41CF-9FD7-EA9F7E93E8DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B2658D-4054-4F3F-824C-28F856F70BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/src/test/resources/ImportTemplate/Checksum - Flat File-SQL.xlsx
+++ b/src/test/resources/ImportTemplate/Checksum - Flat File-SQL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B2658D-4054-4F3F-824C-28F856F70BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC24C538-7FF7-4D53-9383-C71862EBE6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
     <t>|</t>
   </si>
   <si>
-    <t>R00_FlatFile-SQL_Checksum</t>
+    <t>Checksum_ImportSQL--File-FlatFile-SQL_Customer</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Checksum - Flat File-SQL.xlsx
+++ b/src/test/resources/ImportTemplate/Checksum - Flat File-SQL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC24C538-7FF7-4D53-9383-C71862EBE6CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768B3291-C708-4A38-987A-33D74F165308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
     <t>|</t>
   </si>
   <si>
-    <t>Checksum_ImportSQL--File-FlatFile-SQL_Customer</t>
+    <t>Checksum_ImportSQL__File_FlatFile_SQL_Customer</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Checksum - Flat File-SQL.xlsx
+++ b/src/test/resources/ImportTemplate/Checksum - Flat File-SQL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768B3291-C708-4A38-987A-33D74F165308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56D7C0D-4EB8-40DA-B8E5-609F1ED2DC08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>ruleName</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>Checksum_ImportSQL__File_FlatFile_SQL_Customer</t>
+  </si>
+  <si>
+    <t>select count(*) as target_count from tblname_1751280108339</t>
   </si>
 </sst>
 </file>
@@ -523,7 +526,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
         <v>22</v>
